--- a/malaysia-org-contacts/马来西亚商会工商团体通讯录_2026-10-30.xlsx
+++ b/malaysia-org-contacts/马来西亚商会工商团体通讯录_2026-10-30.xlsx
@@ -1054,7 +1054,7 @@
       <c r="I2" s="6" t="inlineStr"/>
       <c r="J2" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 7784 8136</t>
+          <t>+60 3-7784 8136</t>
         </is>
       </c>
       <c r="K2" s="6" t="inlineStr">
@@ -1120,7 +1120,7 @@
       <c r="I3" s="8" t="inlineStr"/>
       <c r="J3" s="8" t="inlineStr">
         <is>
-          <t>+60 6 – 767 3533</t>
+          <t>+60 6-767 3533</t>
         </is>
       </c>
       <c r="K3" s="8" t="inlineStr">
@@ -1186,7 +1186,7 @@
       <c r="I4" s="6" t="inlineStr"/>
       <c r="J4" s="6" t="inlineStr">
         <is>
-          <t>+60 4 – 261 2288</t>
+          <t>+60 4-261 2288</t>
         </is>
       </c>
       <c r="K4" s="6" t="inlineStr">
@@ -1244,7 +1244,7 @@
       <c r="I5" s="8" t="inlineStr"/>
       <c r="J5" s="8" t="inlineStr">
         <is>
-          <t>+60 9 – 743 3827</t>
+          <t>+60 9-743 3827</t>
         </is>
       </c>
       <c r="K5" s="8" t="inlineStr">
@@ -1306,7 +1306,7 @@
       <c r="I6" s="6" t="inlineStr"/>
       <c r="J6" s="6" t="inlineStr">
         <is>
-          <t>+60 5 – 366 2688</t>
+          <t>+60 5-366 2688</t>
         </is>
       </c>
       <c r="K6" s="6" t="inlineStr">
@@ -1368,7 +1368,7 @@
       <c r="I7" s="8" t="inlineStr"/>
       <c r="J7" s="8" t="inlineStr">
         <is>
-          <t>+60 86 – 339 951</t>
+          <t>+60 86-339 951</t>
         </is>
       </c>
       <c r="K7" s="8" t="inlineStr">
@@ -1430,7 +1430,7 @@
       <c r="I8" s="6" t="inlineStr"/>
       <c r="J8" s="6" t="inlineStr">
         <is>
-          <t>+60 7 – 361 9696</t>
+          <t>+60 7-361 9696</t>
         </is>
       </c>
       <c r="K8" s="6" t="inlineStr">
@@ -1492,7 +1492,7 @@
       <c r="I9" s="8" t="inlineStr"/>
       <c r="J9" s="8" t="inlineStr">
         <is>
-          <t>+60 9 – 329 1001</t>
+          <t>+60 9-329 1001</t>
         </is>
       </c>
       <c r="K9" s="8" t="inlineStr">
@@ -1554,7 +1554,7 @@
       <c r="I10" s="6" t="inlineStr"/>
       <c r="J10" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 6034 5566</t>
+          <t>+60 3-6034 5566</t>
         </is>
       </c>
       <c r="K10" s="6" t="inlineStr">
@@ -1616,7 +1616,7 @@
       <c r="I11" s="8" t="inlineStr"/>
       <c r="J11" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 2166 2303</t>
+          <t>+60 3-2166 2303</t>
         </is>
       </c>
       <c r="K11" s="8" t="inlineStr">
@@ -1678,7 +1678,7 @@
       <c r="I12" s="6" t="inlineStr"/>
       <c r="J12" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 7728 8818</t>
+          <t>+60 3-7728 8818</t>
         </is>
       </c>
       <c r="K12" s="6" t="inlineStr">
@@ -1740,7 +1740,7 @@
       <c r="I13" s="8" t="inlineStr"/>
       <c r="J13" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 7980 3094</t>
+          <t>+60 3-7980 3094</t>
         </is>
       </c>
       <c r="K13" s="8" t="inlineStr">
@@ -1806,7 +1806,7 @@
       <c r="I14" s="6" t="inlineStr"/>
       <c r="J14" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 6201 6208</t>
+          <t>+60 3-6201 6208</t>
         </is>
       </c>
       <c r="K14" s="6" t="inlineStr">
@@ -1868,7 +1868,7 @@
       <c r="I15" s="8" t="inlineStr"/>
       <c r="J15" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 2166 8662</t>
+          <t>+60 3-2166 8662</t>
         </is>
       </c>
       <c r="K15" s="8" t="inlineStr">
@@ -1930,7 +1930,7 @@
       <c r="I16" s="6" t="inlineStr"/>
       <c r="J16" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 3291 2689</t>
+          <t>+60 3-3291 2689</t>
         </is>
       </c>
       <c r="K16" s="6" t="inlineStr">
@@ -1992,7 +1992,7 @@
       <c r="I17" s="8" t="inlineStr"/>
       <c r="J17" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 431 7363</t>
+          <t>+60 7-431 7363</t>
         </is>
       </c>
       <c r="K17" s="8" t="inlineStr">
@@ -2054,7 +2054,7 @@
       <c r="I18" s="6" t="inlineStr"/>
       <c r="J18" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 7880 5520</t>
+          <t>+60 3-7880 5520</t>
         </is>
       </c>
       <c r="K18" s="6" t="inlineStr">
@@ -2116,7 +2116,7 @@
       <c r="I19" s="8" t="inlineStr"/>
       <c r="J19" s="8" t="inlineStr">
         <is>
-          <t>+60 9 – 631 6312</t>
+          <t>+60 9-631 6312</t>
         </is>
       </c>
       <c r="K19" s="8" t="inlineStr">
@@ -2172,11 +2172,7 @@
         </is>
       </c>
       <c r="I20" s="6" t="inlineStr"/>
-      <c r="J20" s="6" t="inlineStr">
-        <is>
-          <t>0 88 – 2523 12/0 88 – 2252 99</t>
-        </is>
-      </c>
+      <c r="J20" s="6" t="inlineStr"/>
       <c r="K20" s="6" t="inlineStr">
         <is>
           <t>yslui84@gmail.com</t>
@@ -2232,7 +2228,7 @@
       <c r="I21" s="8" t="inlineStr"/>
       <c r="J21" s="8" t="inlineStr">
         <is>
-          <t>+60 4 – 733 3688/+60 4 -730 0612</t>
+          <t>+60 4-733 3688 / +60 4-730 0612</t>
         </is>
       </c>
       <c r="K21" s="8" t="inlineStr">
@@ -2290,7 +2286,7 @@
       <c r="I22" s="6" t="inlineStr"/>
       <c r="J22" s="6" t="inlineStr">
         <is>
-          <t>+60 7 – 776 8121</t>
+          <t>+60 7-776 8121</t>
         </is>
       </c>
       <c r="K22" s="6" t="inlineStr">
@@ -2348,7 +2344,7 @@
       <c r="I23" s="8" t="inlineStr"/>
       <c r="J23" s="8" t="inlineStr">
         <is>
-          <t>+60 5 – 820 6666</t>
+          <t>+60 5-820 6666</t>
         </is>
       </c>
       <c r="K23" s="8" t="inlineStr">
@@ -2406,7 +2402,7 @@
       <c r="I24" s="6" t="inlineStr"/>
       <c r="J24" s="6" t="inlineStr">
         <is>
-          <t>+60 6 – 231 0333</t>
+          <t>+60 6-231 0333</t>
         </is>
       </c>
       <c r="K24" s="6" t="inlineStr">
@@ -2464,7 +2460,7 @@
       <c r="I25" s="8" t="inlineStr"/>
       <c r="J25" s="8" t="inlineStr">
         <is>
-          <t>+60 4 – 976 2504</t>
+          <t>+60 4-976 2504</t>
         </is>
       </c>
       <c r="K25" s="8" t="inlineStr">
@@ -2526,7 +2522,7 @@
       <c r="I26" s="6" t="inlineStr"/>
       <c r="J26" s="6" t="inlineStr">
         <is>
-          <t>+60 12 339 2925</t>
+          <t>+60 12-339 2925</t>
         </is>
       </c>
       <c r="K26" s="6" t="inlineStr">
@@ -2588,7 +2584,7 @@
       <c r="I27" s="8" t="inlineStr"/>
       <c r="J27" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 3168 6842</t>
+          <t>+60 3-3168 6842</t>
         </is>
       </c>
       <c r="K27" s="8" t="inlineStr">
@@ -2650,7 +2646,7 @@
       <c r="I28" s="6" t="inlineStr"/>
       <c r="J28" s="6" t="inlineStr">
         <is>
-          <t>+60 82 -578 811</t>
+          <t>+60 82-578 811</t>
         </is>
       </c>
       <c r="K28" s="6" t="inlineStr">
@@ -2712,7 +2708,7 @@
       <c r="I29" s="8" t="inlineStr"/>
       <c r="J29" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 773 9188</t>
+          <t>+60 7-773 9188</t>
         </is>
       </c>
       <c r="K29" s="8" t="inlineStr">
@@ -2770,7 +2766,7 @@
       <c r="I30" s="6" t="inlineStr"/>
       <c r="J30" s="6" t="inlineStr">
         <is>
-          <t>+60 7 – 550 6313</t>
+          <t>+60 7-550 6313</t>
         </is>
       </c>
       <c r="K30" s="6" t="inlineStr">
@@ -2832,7 +2828,7 @@
       <c r="I31" s="8" t="inlineStr"/>
       <c r="J31" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 8732 2626</t>
+          <t>+60 3-8732 2626</t>
         </is>
       </c>
       <c r="K31" s="8" t="inlineStr">
@@ -2894,7 +2890,7 @@
       <c r="I32" s="6" t="inlineStr"/>
       <c r="J32" s="6" t="inlineStr">
         <is>
-          <t>+60 9 – 743 3694</t>
+          <t>+60 9-743 3694</t>
         </is>
       </c>
       <c r="K32" s="6" t="inlineStr">
@@ -2956,7 +2952,7 @@
       <c r="I33" s="8" t="inlineStr"/>
       <c r="J33" s="8" t="inlineStr">
         <is>
-          <t>+60 6 – 284 8877</t>
+          <t>+60 6-284 8877</t>
         </is>
       </c>
       <c r="K33" s="8" t="inlineStr">
@@ -3014,7 +3010,7 @@
       <c r="I34" s="6" t="inlineStr"/>
       <c r="J34" s="6" t="inlineStr">
         <is>
-          <t>+60 9 – 622 9493</t>
+          <t>+60 9-622 9493</t>
         </is>
       </c>
       <c r="K34" s="6" t="inlineStr">
@@ -3076,7 +3072,7 @@
       <c r="I35" s="8" t="inlineStr"/>
       <c r="J35" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 4270 6420</t>
+          <t>+60 3-4270 6420</t>
         </is>
       </c>
       <c r="K35" s="8" t="inlineStr">
@@ -3134,7 +3130,7 @@
       <c r="I36" s="6" t="inlineStr"/>
       <c r="J36" s="6" t="inlineStr">
         <is>
-          <t>+60 5 – 757 7201</t>
+          <t>+60 5-757 7201</t>
         </is>
       </c>
       <c r="K36" s="6" t="inlineStr">
@@ -3188,7 +3184,7 @@
       <c r="I37" s="8" t="inlineStr"/>
       <c r="J37" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 431 9929</t>
+          <t>+60 7-431 9929</t>
         </is>
       </c>
       <c r="K37" s="8" t="inlineStr">
@@ -3250,7 +3246,7 @@
       <c r="I38" s="6" t="inlineStr"/>
       <c r="J38" s="6" t="inlineStr">
         <is>
-          <t>+60 7 – 652 1997</t>
+          <t>+60 7-652 1997</t>
         </is>
       </c>
       <c r="K38" s="6" t="inlineStr">
@@ -3308,7 +3304,7 @@
       <c r="I39" s="8" t="inlineStr"/>
       <c r="J39" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 410 2112</t>
+          <t>+60 7-410 2112</t>
         </is>
       </c>
       <c r="K39" s="8" t="inlineStr">
@@ -3370,7 +3366,7 @@
       <c r="I40" s="6" t="inlineStr"/>
       <c r="J40" s="6" t="inlineStr">
         <is>
-          <t>+60 5 – 8012 663</t>
+          <t>+60 5-801 2663</t>
         </is>
       </c>
       <c r="K40" s="6" t="inlineStr">
@@ -3432,7 +3428,7 @@
       <c r="I41" s="8" t="inlineStr"/>
       <c r="J41" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 2110 6822</t>
+          <t>+60 3-2110 6822</t>
         </is>
       </c>
       <c r="K41" s="8" t="inlineStr">
@@ -3494,7 +3490,7 @@
       <c r="I42" s="6" t="inlineStr"/>
       <c r="J42" s="6" t="inlineStr">
         <is>
-          <t>+60 12 – 886 6666</t>
+          <t>+60 12-886 6666</t>
         </is>
       </c>
       <c r="K42" s="6" t="inlineStr">
@@ -3552,7 +3548,7 @@
       <c r="I43" s="8" t="inlineStr"/>
       <c r="J43" s="8" t="inlineStr">
         <is>
-          <t>+60 4 – 262 4412</t>
+          <t>+60 4-262 4412</t>
         </is>
       </c>
       <c r="K43" s="8" t="inlineStr">
@@ -3614,7 +3610,7 @@
       <c r="I44" s="6" t="inlineStr"/>
       <c r="J44" s="6" t="inlineStr">
         <is>
-          <t>+60 12 – 443 8888</t>
+          <t>+60 12-443 8888</t>
         </is>
       </c>
       <c r="K44" s="6" t="inlineStr">
@@ -3676,7 +3672,7 @@
       <c r="I45" s="8" t="inlineStr"/>
       <c r="J45" s="8" t="inlineStr">
         <is>
-          <t>+60 5 – 312 7777</t>
+          <t>+60 5-312 7777</t>
         </is>
       </c>
       <c r="K45" s="8" t="inlineStr">
@@ -3734,7 +3730,7 @@
       <c r="I46" s="6" t="inlineStr"/>
       <c r="J46" s="6" t="inlineStr">
         <is>
-          <t>+60 12 – 2900 089</t>
+          <t>+60 12-290 0089</t>
         </is>
       </c>
       <c r="K46" s="6" t="inlineStr">
@@ -3796,7 +3792,7 @@
       <c r="I47" s="8" t="inlineStr"/>
       <c r="J47" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 777 1836</t>
+          <t>+60 7-777 1836</t>
         </is>
       </c>
       <c r="K47" s="8" t="inlineStr">
@@ -3858,7 +3854,7 @@
       <c r="I48" s="6" t="inlineStr"/>
       <c r="J48" s="6" t="inlineStr">
         <is>
-          <t>+60 3 – 7859 6841</t>
+          <t>+60 3-7859 6841</t>
         </is>
       </c>
       <c r="K48" s="6" t="inlineStr">
@@ -3916,7 +3912,7 @@
       <c r="I49" s="8" t="inlineStr"/>
       <c r="J49" s="8" t="inlineStr">
         <is>
-          <t>+60 6 – 282 8189/+601 7 – 7100 231</t>
+          <t>+60 6-282 8189</t>
         </is>
       </c>
       <c r="K49" s="8" t="inlineStr">
@@ -3978,7 +3974,7 @@
       <c r="I50" s="6" t="inlineStr"/>
       <c r="J50" s="6" t="inlineStr">
         <is>
-          <t>+60 9 – 267 2288/+60 9 – 267 1288</t>
+          <t>+60 9-267 2288 / +60 9-267 1288</t>
         </is>
       </c>
       <c r="K50" s="6" t="inlineStr">
@@ -4040,7 +4036,7 @@
       <c r="I51" s="8" t="inlineStr"/>
       <c r="J51" s="8" t="inlineStr">
         <is>
-          <t>+60 3 – 2380 0155</t>
+          <t>+60 3-2380 0155</t>
         </is>
       </c>
       <c r="K51" s="8" t="inlineStr">
@@ -4098,7 +4094,7 @@
       <c r="I52" s="6" t="inlineStr"/>
       <c r="J52" s="6" t="inlineStr">
         <is>
-          <t>+60 9 – 765 5339</t>
+          <t>+60 9-765 5339</t>
         </is>
       </c>
       <c r="K52" s="6" t="inlineStr">
@@ -4156,7 +4152,7 @@
       <c r="I53" s="8" t="inlineStr"/>
       <c r="J53" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 951 1777</t>
+          <t>+60 7-951 1777</t>
         </is>
       </c>
       <c r="K53" s="8" t="inlineStr">
@@ -4218,7 +4214,7 @@
       <c r="I54" s="6" t="inlineStr"/>
       <c r="J54" s="6" t="inlineStr">
         <is>
-          <t>+60 9 – 617 3538</t>
+          <t>+60 9-617 3538</t>
         </is>
       </c>
       <c r="K54" s="6" t="inlineStr"/>
@@ -4276,7 +4272,7 @@
       <c r="I55" s="8" t="inlineStr"/>
       <c r="J55" s="8" t="inlineStr">
         <is>
-          <t>+60 7 – 432 7333</t>
+          <t>+60 7-432 7333</t>
         </is>
       </c>
       <c r="K55" s="8" t="inlineStr">
@@ -4338,7 +4334,7 @@
       <c r="I56" s="6" t="inlineStr"/>
       <c r="J56" s="6" t="inlineStr">
         <is>
-          <t>+60 12 – 296 2386</t>
+          <t>+60 12-296 2386</t>
         </is>
       </c>
       <c r="K56" s="6" t="inlineStr">
@@ -11152,7 +11148,7 @@
       <c r="I233" s="8" t="inlineStr"/>
       <c r="J233" s="8" t="inlineStr">
         <is>
-          <t>+60 3 7784 8136</t>
+          <t>+60 3-7784 8136</t>
         </is>
       </c>
       <c r="K233" s="8" t="inlineStr"/>
@@ -11202,7 +11198,7 @@
       <c r="I234" s="6" t="inlineStr"/>
       <c r="J234" s="6" t="inlineStr">
         <is>
-          <t>+60 3 7880 5520</t>
+          <t>+60 3-7880 5520</t>
         </is>
       </c>
       <c r="K234" s="6" t="inlineStr"/>
@@ -11252,7 +11248,7 @@
       <c r="I235" s="8" t="inlineStr"/>
       <c r="J235" s="8" t="inlineStr">
         <is>
-          <t>+60 3 7728 8878</t>
+          <t>+60 3-7728 8878</t>
         </is>
       </c>
       <c r="K235" s="8" t="inlineStr"/>
@@ -11302,7 +11298,7 @@
       <c r="I236" s="6" t="inlineStr"/>
       <c r="J236" s="6" t="inlineStr">
         <is>
-          <t>+60 3 7980 3094</t>
+          <t>+60 3-7980 3094</t>
         </is>
       </c>
       <c r="K236" s="6" t="inlineStr"/>
@@ -11352,7 +11348,7 @@
       <c r="I237" s="8" t="inlineStr"/>
       <c r="J237" s="8" t="inlineStr">
         <is>
-          <t>+60 3 2142 1262</t>
+          <t>+60 3-2142 1262</t>
         </is>
       </c>
       <c r="K237" s="8" t="inlineStr"/>
@@ -11402,7 +11398,7 @@
       <c r="I238" s="6" t="inlineStr"/>
       <c r="J238" s="6" t="inlineStr">
         <is>
-          <t>+60 3 8732 2626</t>
+          <t>+60 3-8732 2626</t>
         </is>
       </c>
       <c r="K238" s="6" t="inlineStr"/>
@@ -11452,7 +11448,7 @@
       <c r="I239" s="8" t="inlineStr"/>
       <c r="J239" s="8" t="inlineStr">
         <is>
-          <t>+60 3 5512 5128</t>
+          <t>+60 3-5512 5128</t>
         </is>
       </c>
       <c r="K239" s="8" t="inlineStr"/>
@@ -11502,7 +11498,7 @@
       <c r="I240" s="6" t="inlineStr"/>
       <c r="J240" s="6" t="inlineStr">
         <is>
-          <t>+60 3 2161 2588</t>
+          <t>+60 3-2161 2588</t>
         </is>
       </c>
       <c r="K240" s="6" t="inlineStr"/>
@@ -11548,7 +11544,7 @@
       <c r="I241" s="8" t="inlineStr"/>
       <c r="J241" s="8" t="inlineStr">
         <is>
-          <t>+60 3 2166 8662</t>
+          <t>+60 3-2166 8662</t>
         </is>
       </c>
       <c r="K241" s="8" t="inlineStr"/>
@@ -11598,7 +11594,7 @@
       <c r="I242" s="6" t="inlineStr"/>
       <c r="J242" s="6" t="inlineStr">
         <is>
-          <t>+60 3 6140 1111</t>
+          <t>+60 3-6140 1111</t>
         </is>
       </c>
       <c r="K242" s="6" t="inlineStr"/>
@@ -11640,7 +11636,7 @@
       <c r="I243" s="8" t="inlineStr"/>
       <c r="J243" s="8" t="inlineStr">
         <is>
-          <t>+60 3 6201 6208</t>
+          <t>+60 3-6201 6208</t>
         </is>
       </c>
       <c r="K243" s="8" t="inlineStr"/>
@@ -11686,7 +11682,7 @@
       <c r="I244" s="6" t="inlineStr"/>
       <c r="J244" s="6" t="inlineStr">
         <is>
-          <t>+60 3 5633 1612</t>
+          <t>+60 3-5633 1612</t>
         </is>
       </c>
       <c r="K244" s="6" t="inlineStr"/>
@@ -11736,7 +11732,7 @@
       <c r="I245" s="8" t="inlineStr"/>
       <c r="J245" s="8" t="inlineStr">
         <is>
-          <t>+60 3 7965 9822</t>
+          <t>+60 3-7965 9822</t>
         </is>
       </c>
       <c r="K245" s="8" t="inlineStr"/>
@@ -11786,7 +11782,7 @@
       <c r="I246" s="6" t="inlineStr"/>
       <c r="J246" s="6" t="inlineStr">
         <is>
-          <t>+60 11 3330 3130</t>
+          <t>+60 11-3330 3130</t>
         </is>
       </c>
       <c r="K246" s="6" t="inlineStr"/>
@@ -11836,7 +11832,7 @@
       <c r="I247" s="8" t="inlineStr"/>
       <c r="J247" s="8" t="inlineStr">
         <is>
-          <t>+60 3 2110 6822</t>
+          <t>+60 3-2110 6822</t>
         </is>
       </c>
       <c r="K247" s="8" t="inlineStr"/>
@@ -11882,7 +11878,7 @@
       <c r="I248" s="6" t="inlineStr"/>
       <c r="J248" s="6" t="inlineStr">
         <is>
-          <t>+60 3 3342 2862</t>
+          <t>+60 3-3342 2862</t>
         </is>
       </c>
       <c r="K248" s="6" t="inlineStr"/>
@@ -11924,7 +11920,7 @@
       <c r="I249" s="8" t="inlineStr"/>
       <c r="J249" s="8" t="inlineStr">
         <is>
-          <t>+60 3 4291 9233</t>
+          <t>+60 3-4291 9233</t>
         </is>
       </c>
       <c r="K249" s="8" t="inlineStr"/>
@@ -11970,7 +11966,7 @@
       <c r="I250" s="6" t="inlineStr"/>
       <c r="J250" s="6" t="inlineStr">
         <is>
-          <t>+60 7 353 5331</t>
+          <t>+60 7-353 5331</t>
         </is>
       </c>
       <c r="K250" s="6" t="inlineStr"/>
@@ -12020,7 +12016,7 @@
       <c r="I251" s="8" t="inlineStr"/>
       <c r="J251" s="8" t="inlineStr">
         <is>
-          <t>+60 3 7783 4648</t>
+          <t>+60 3-7783 4648</t>
         </is>
       </c>
       <c r="K251" s="8" t="inlineStr"/>
@@ -12066,7 +12062,7 @@
       <c r="I252" s="6" t="inlineStr"/>
       <c r="J252" s="6" t="inlineStr">
         <is>
-          <t>+60 3 2785 0551</t>
+          <t>+60 3-2785 0551</t>
         </is>
       </c>
       <c r="K252" s="6" t="inlineStr"/>
@@ -12116,7 +12112,7 @@
       <c r="I253" s="8" t="inlineStr"/>
       <c r="J253" s="8" t="inlineStr">
         <is>
-          <t>+60 3 5634 1436</t>
+          <t>+60 3-5634 1436</t>
         </is>
       </c>
       <c r="K253" s="8" t="inlineStr"/>
@@ -12166,7 +12162,7 @@
       <c r="I254" s="6" t="inlineStr"/>
       <c r="J254" s="6" t="inlineStr">
         <is>
-          <t>+60 3 7610 8858</t>
+          <t>+60 3-7610 8858</t>
         </is>
       </c>
       <c r="K254" s="6" t="inlineStr"/>
@@ -12250,7 +12246,7 @@
       <c r="I256" s="6" t="inlineStr"/>
       <c r="J256" s="6" t="inlineStr">
         <is>
-          <t>+60 3 9221 3188</t>
+          <t>+60 3-9221 3188</t>
         </is>
       </c>
       <c r="K256" s="6" t="inlineStr"/>
@@ -12300,7 +12296,7 @@
       <c r="I257" s="8" t="inlineStr"/>
       <c r="J257" s="8" t="inlineStr">
         <is>
-          <t>+60 3 6251 1133</t>
+          <t>+60 3-6251 1133</t>
         </is>
       </c>
       <c r="K257" s="8" t="inlineStr"/>
@@ -12350,7 +12346,7 @@
       <c r="I258" s="6" t="inlineStr"/>
       <c r="J258" s="6" t="inlineStr">
         <is>
-          <t>+60 3 5891 1157</t>
+          <t>+60 3-5891 1157</t>
         </is>
       </c>
       <c r="K258" s="6" t="inlineStr"/>
@@ -12400,7 +12396,7 @@
       <c r="I259" s="8" t="inlineStr"/>
       <c r="J259" s="8" t="inlineStr">
         <is>
-          <t>+60 3 8022 3333</t>
+          <t>+60 3-8022 3333</t>
         </is>
       </c>
       <c r="K259" s="8" t="inlineStr"/>
@@ -12450,7 +12446,7 @@
       <c r="I260" s="6" t="inlineStr"/>
       <c r="J260" s="6" t="inlineStr">
         <is>
-          <t>+60 3 2242 4299</t>
+          <t>+60 3-2242 4299</t>
         </is>
       </c>
       <c r="K260" s="6" t="inlineStr"/>
@@ -12500,7 +12496,7 @@
       <c r="I261" s="8" t="inlineStr"/>
       <c r="J261" s="8" t="inlineStr">
         <is>
-          <t>+60 3 5525 4133</t>
+          <t>+60 3-5525 4133</t>
         </is>
       </c>
       <c r="K261" s="8" t="inlineStr"/>
@@ -12550,7 +12546,7 @@
       <c r="I262" s="6" t="inlineStr"/>
       <c r="J262" s="6" t="inlineStr">
         <is>
-          <t>+60 3 7783 1811</t>
+          <t>+60 3-7783 1811</t>
         </is>
       </c>
       <c r="K262" s="6" t="inlineStr"/>
@@ -12600,7 +12596,7 @@
       <c r="I263" s="8" t="inlineStr"/>
       <c r="J263" s="8" t="inlineStr">
         <is>
-          <t>+60 3 6145 7777</t>
+          <t>+60 3-6145 7777</t>
         </is>
       </c>
       <c r="K263" s="8" t="inlineStr"/>
@@ -12650,7 +12646,7 @@
       <c r="I264" s="6" t="inlineStr"/>
       <c r="J264" s="6" t="inlineStr">
         <is>
-          <t>+60 3 3279 1773</t>
+          <t>+60 3-3279 1773</t>
         </is>
       </c>
       <c r="K264" s="6" t="inlineStr"/>
@@ -12700,7 +12696,7 @@
       <c r="I265" s="8" t="inlineStr"/>
       <c r="J265" s="8" t="inlineStr">
         <is>
-          <t>+60 3 5882 6882</t>
+          <t>+60 3-5882 6882</t>
         </is>
       </c>
       <c r="K265" s="8" t="inlineStr"/>
@@ -12750,7 +12746,7 @@
       <c r="I266" s="6" t="inlineStr"/>
       <c r="J266" s="6" t="inlineStr">
         <is>
-          <t>+60 3 6286 1000</t>
+          <t>+60 3-6286 1000</t>
         </is>
       </c>
       <c r="K266" s="6" t="inlineStr"/>
@@ -12792,7 +12788,7 @@
       <c r="I267" s="8" t="inlineStr"/>
       <c r="J267" s="8" t="inlineStr">
         <is>
-          <t>+60 3 8961 3111</t>
+          <t>+60 3-8961 3111</t>
         </is>
       </c>
       <c r="K267" s="8" t="inlineStr"/>
@@ -12838,7 +12834,7 @@
       <c r="I268" s="6" t="inlineStr"/>
       <c r="J268" s="6" t="inlineStr">
         <is>
-          <t>+60 3 5633 0408</t>
+          <t>+60 3-5633 0408</t>
         </is>
       </c>
       <c r="K268" s="6" t="inlineStr"/>
@@ -12888,7 +12884,7 @@
       <c r="I269" s="8" t="inlineStr"/>
       <c r="J269" s="8" t="inlineStr">
         <is>
-          <t>+60 3 8076 2700</t>
+          <t>+60 3-8076 2700</t>
         </is>
       </c>
       <c r="K269" s="8" t="inlineStr"/>
@@ -12938,7 +12934,7 @@
       <c r="I270" s="6" t="inlineStr"/>
       <c r="J270" s="6" t="inlineStr">
         <is>
-          <t>+60 3 3187 1177 / 1178</t>
+          <t>+60 3-3187 1177</t>
         </is>
       </c>
       <c r="K270" s="6" t="inlineStr"/>
@@ -12988,7 +12984,7 @@
       <c r="I271" s="8" t="inlineStr"/>
       <c r="J271" s="8" t="inlineStr">
         <is>
-          <t>+60 6 799 5255</t>
+          <t>+60 6-799 5255</t>
         </is>
       </c>
       <c r="K271" s="8" t="inlineStr"/>
@@ -13034,7 +13030,7 @@
       <c r="I272" s="6" t="inlineStr"/>
       <c r="J272" s="6" t="inlineStr">
         <is>
-          <t>+60 3 2148 3811</t>
+          <t>+60 3-2148 3811</t>
         </is>
       </c>
       <c r="K272" s="6" t="inlineStr"/>
@@ -19581,12 +19577,12 @@
       </c>
       <c r="I456" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4230006</t>
+          <t>+60 12-423 0006</t>
         </is>
       </c>
       <c r="J456" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7345888</t>
+          <t>+60 4-734 5888</t>
         </is>
       </c>
       <c r="K456" s="6" t="inlineStr">
@@ -19631,12 +19627,12 @@
       <c r="H457" s="8" t="inlineStr"/>
       <c r="I457" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4504285</t>
+          <t>+60 19-450 4285</t>
         </is>
       </c>
       <c r="J457" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7330288 , / +604 - 7330289</t>
+          <t>+60 4-733 0288 / +60 4-733 0289</t>
         </is>
       </c>
       <c r="K457" s="8" t="inlineStr">
@@ -19685,12 +19681,12 @@
       </c>
       <c r="I458" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4407296</t>
+          <t>+60 19-440 7296</t>
         </is>
       </c>
       <c r="J458" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7314872 , / +604 - 7311989</t>
+          <t>+60 4-731 4872 / +60 4-731 1989</t>
         </is>
       </c>
       <c r="K458" s="6" t="inlineStr">
@@ -19743,12 +19739,12 @@
       </c>
       <c r="I459" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4252563</t>
+          <t>+60 12-425 2563</t>
         </is>
       </c>
       <c r="J459" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7307688 , / +604 - 7313689 , / +604 - 7308684</t>
+          <t>+60 4-730 7688 / +60 4-731 3689 / +60 4-730 8684</t>
         </is>
       </c>
       <c r="K459" s="8" t="inlineStr">
@@ -19801,12 +19797,12 @@
       </c>
       <c r="I460" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4011283</t>
+          <t>+60 12-401 1283</t>
         </is>
       </c>
       <c r="J460" s="6" t="inlineStr">
         <is>
-          <t>+604 - 4215737</t>
+          <t>+60 4-421 5737</t>
         </is>
       </c>
       <c r="K460" s="6" t="inlineStr">
@@ -19859,12 +19855,12 @@
       </c>
       <c r="I461" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4107607</t>
+          <t>+60 12-410 7607</t>
         </is>
       </c>
       <c r="J461" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7311989</t>
+          <t>+60 4-731 1989</t>
         </is>
       </c>
       <c r="K461" s="8" t="inlineStr">
@@ -19917,12 +19913,12 @@
       </c>
       <c r="I462" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4406515</t>
+          <t>+60 19-440 6515</t>
         </is>
       </c>
       <c r="J462" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7333688 , / +604 - 7300612</t>
+          <t>+60 4-733 3688 / +60 4-730 0612</t>
         </is>
       </c>
       <c r="K462" s="6" t="inlineStr">
@@ -19975,12 +19971,12 @@
       </c>
       <c r="I463" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4413922</t>
+          <t>+60 19-441 3922</t>
         </is>
       </c>
       <c r="J463" s="8" t="inlineStr">
         <is>
-          <t>+604 - 9178799</t>
+          <t>+60 4-917 8799</t>
         </is>
       </c>
       <c r="K463" s="8" t="inlineStr">
@@ -20033,12 +20029,12 @@
       </c>
       <c r="I464" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4501026</t>
+          <t>+60 19-450 1026</t>
         </is>
       </c>
       <c r="J464" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7716804 , / +604 - 7723066</t>
+          <t>+60 4-771 6804 / +60 4-772 3066</t>
         </is>
       </c>
       <c r="K464" s="6" t="inlineStr">
@@ -20091,12 +20087,12 @@
       </c>
       <c r="I465" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4212079</t>
+          <t>+60 12-421 2079</t>
         </is>
       </c>
       <c r="J465" s="8" t="inlineStr">
         <is>
-          <t>+604 - 4218801</t>
+          <t>+60 4-421 8801</t>
         </is>
       </c>
       <c r="K465" s="8" t="inlineStr">
@@ -20149,12 +20145,12 @@
       </c>
       <c r="I466" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4006633</t>
+          <t>+60 12-400 6633</t>
         </is>
       </c>
       <c r="J466" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7773363</t>
+          <t>+60 4-777 3363</t>
         </is>
       </c>
       <c r="K466" s="6" t="inlineStr">
@@ -20207,12 +20203,12 @@
       </c>
       <c r="I467" s="8" t="inlineStr">
         <is>
-          <t>+6017 - 4697789</t>
+          <t>+60 17-469 7789</t>
         </is>
       </c>
       <c r="J467" s="8" t="inlineStr">
         <is>
-          <t>+604 - 9174351, / +604 - 916 1268</t>
+          <t>+60 4-917 4351 / +60 4-916 1268</t>
         </is>
       </c>
       <c r="K467" s="8" t="inlineStr">
@@ -20265,12 +20261,12 @@
       </c>
       <c r="I468" s="6" t="inlineStr">
         <is>
-          <t>+6017 - 4192388</t>
+          <t>+60 17-419 2388</t>
         </is>
       </c>
       <c r="J468" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7302945, / +604 - 7302946, / +604 - 7302370</t>
+          <t>+60 4-730 2945 / +60 4-730 2946 / +60 4-730 2370</t>
         </is>
       </c>
       <c r="K468" s="6" t="inlineStr">
@@ -20319,12 +20315,12 @@
       <c r="H469" s="8" t="inlineStr"/>
       <c r="I469" s="8" t="inlineStr">
         <is>
-          <t>+012 - 4737141</t>
+          <t>+60 12-473 7141</t>
         </is>
       </c>
       <c r="J469" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7311109, / +604 - 7322999</t>
+          <t>+60 4-731 1109 / +60 4-732 2999</t>
         </is>
       </c>
       <c r="K469" s="8" t="inlineStr">
@@ -20377,12 +20373,12 @@
       </c>
       <c r="I470" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4330039</t>
+          <t>+60 12-433 0039</t>
         </is>
       </c>
       <c r="J470" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7312288 , / +604 - 7301888</t>
+          <t>+60 4-731 2288 / +60 4-730 1888</t>
         </is>
       </c>
       <c r="K470" s="6" t="inlineStr">
@@ -20435,12 +20431,12 @@
       </c>
       <c r="I471" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 5996185</t>
+          <t>+60 12-599 6185</t>
         </is>
       </c>
       <c r="J471" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7333067</t>
+          <t>+60 4-733 3067</t>
         </is>
       </c>
       <c r="K471" s="8" t="inlineStr"/>
@@ -20485,12 +20481,12 @@
       <c r="H472" s="6" t="inlineStr"/>
       <c r="I472" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4323388</t>
+          <t>+60 12-432 3388</t>
         </is>
       </c>
       <c r="J472" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7323788</t>
+          <t>+60 4-732 3788</t>
         </is>
       </c>
       <c r="K472" s="6" t="inlineStr">
@@ -20543,12 +20539,12 @@
       </c>
       <c r="I473" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4719888</t>
+          <t>+60 12-471 9888</t>
         </is>
       </c>
       <c r="J473" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7878888</t>
+          <t>+60 4-787 8888</t>
         </is>
       </c>
       <c r="K473" s="8" t="inlineStr">
@@ -20601,12 +20597,12 @@
       </c>
       <c r="I474" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4824350</t>
+          <t>+60 12-482 4350</t>
         </is>
       </c>
       <c r="J474" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7300948</t>
+          <t>+60 4-730 0948</t>
         </is>
       </c>
       <c r="K474" s="6" t="inlineStr">
@@ -20659,12 +20655,12 @@
       </c>
       <c r="I475" s="8" t="inlineStr">
         <is>
-          <t>+6013 - 4281936</t>
+          <t>+60 13-428 1936</t>
         </is>
       </c>
       <c r="J475" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7822936</t>
+          <t>+60 4-782 2936</t>
         </is>
       </c>
       <c r="K475" s="8" t="inlineStr">
@@ -20717,12 +20713,12 @@
       </c>
       <c r="I476" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 2388732</t>
+          <t>+60 19-238 8732</t>
         </is>
       </c>
       <c r="J476" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7312591</t>
+          <t>+60 4-731 2591</t>
         </is>
       </c>
       <c r="K476" s="6" t="inlineStr">
@@ -20775,12 +20771,12 @@
       </c>
       <c r="I477" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4933666</t>
+          <t>+60 12-493 3666</t>
         </is>
       </c>
       <c r="J477" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7691393</t>
+          <t>+60 4-769 1393</t>
         </is>
       </c>
       <c r="K477" s="8" t="inlineStr">
@@ -20825,12 +20821,12 @@
       <c r="H478" s="6" t="inlineStr"/>
       <c r="I478" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 428 9362</t>
+          <t>+60 12-428 9362</t>
         </is>
       </c>
       <c r="J478" s="6" t="inlineStr">
         <is>
-          <t>+604 - 425 5389</t>
+          <t>+60 4-425 5389</t>
         </is>
       </c>
       <c r="K478" s="6" t="inlineStr">
@@ -20879,12 +20875,12 @@
       </c>
       <c r="I479" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4772333</t>
+          <t>+60 12-477 2333</t>
         </is>
       </c>
       <c r="J479" s="8" t="inlineStr">
         <is>
-          <t>+604 - 9173366</t>
+          <t>+60 4-917 3366</t>
         </is>
       </c>
       <c r="K479" s="8" t="inlineStr">
@@ -20937,12 +20933,12 @@
       </c>
       <c r="I480" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4407369</t>
+          <t>+60 19-440 7369</t>
         </is>
       </c>
       <c r="J480" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7345721</t>
+          <t>+60 4-734 5721</t>
         </is>
       </c>
       <c r="K480" s="6" t="inlineStr">
@@ -20995,12 +20991,12 @@
       </c>
       <c r="I481" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 7500899</t>
+          <t>+60 12-750 0899</t>
         </is>
       </c>
       <c r="J481" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7318125</t>
+          <t>+60 4-731 8125</t>
         </is>
       </c>
       <c r="K481" s="8" t="inlineStr">
@@ -21053,12 +21049,12 @@
       </c>
       <c r="I482" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 2592328</t>
+          <t>+60 19-259 2328</t>
         </is>
       </c>
       <c r="J482" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7355620</t>
+          <t>+60 4-735 5620</t>
         </is>
       </c>
       <c r="K482" s="6" t="inlineStr">
@@ -21111,12 +21107,12 @@
       </c>
       <c r="I483" s="8" t="inlineStr">
         <is>
-          <t>+6016 - 4404826</t>
+          <t>+60 16-440 4826</t>
         </is>
       </c>
       <c r="J483" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7339619</t>
+          <t>+60 4-733 9619</t>
         </is>
       </c>
       <c r="K483" s="8" t="inlineStr">
@@ -21169,12 +21165,12 @@
       </c>
       <c r="I484" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4408819</t>
+          <t>+60 19-440 8819</t>
         </is>
       </c>
       <c r="J484" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7342399</t>
+          <t>+60 4-734 2399</t>
         </is>
       </c>
       <c r="K484" s="6" t="inlineStr">
@@ -21227,12 +21223,12 @@
       </c>
       <c r="I485" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4406525</t>
+          <t>+60 19-440 6525</t>
         </is>
       </c>
       <c r="J485" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7331391 , / +604 - 7323392</t>
+          <t>+60 4-733 1391 / +60 4-732 3392</t>
         </is>
       </c>
       <c r="K485" s="8" t="inlineStr">
@@ -21285,12 +21281,12 @@
       </c>
       <c r="I486" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4443834</t>
+          <t>+60 19-444 3834</t>
         </is>
       </c>
       <c r="J486" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7723388 , / +604 - 7726688</t>
+          <t>+60 4-772 3388 / +60 4-772 6688</t>
         </is>
       </c>
       <c r="K486" s="6" t="inlineStr">
@@ -21339,12 +21335,12 @@
       </c>
       <c r="I487" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4942523</t>
+          <t>+60 12-494 2523</t>
         </is>
       </c>
       <c r="J487" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7336085</t>
+          <t>+60 4-733 6085</t>
         </is>
       </c>
       <c r="K487" s="8" t="inlineStr">
@@ -21397,12 +21393,12 @@
       </c>
       <c r="I488" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4842255</t>
+          <t>+60 12-484 2255</t>
         </is>
       </c>
       <c r="J488" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7313485 , / +604 - 7331487 , / +604 - 7321741</t>
+          <t>+60 4-731 3485 / +60 4-733 1487 / +60 4-732 1741</t>
         </is>
       </c>
       <c r="K488" s="6" t="inlineStr">
@@ -21455,12 +21451,12 @@
       </c>
       <c r="I489" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 5261002</t>
+          <t>+60 12-526 1002</t>
         </is>
       </c>
       <c r="J489" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7312387 , / +604 - 7316449</t>
+          <t>+60 4-731 2387 / +60 4-731 6449</t>
         </is>
       </c>
       <c r="K489" s="8" t="inlineStr">
@@ -21513,12 +21509,12 @@
       </c>
       <c r="I490" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4892348</t>
+          <t>+60 12-489 2348</t>
         </is>
       </c>
       <c r="J490" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7876203</t>
+          <t>+60 4-787 6203</t>
         </is>
       </c>
       <c r="K490" s="6" t="inlineStr">
@@ -21571,12 +21567,12 @@
       </c>
       <c r="I491" s="8" t="inlineStr">
         <is>
-          <t>+6016 - 4218989, 016 - 4988989</t>
+          <t>+60 16-421 8989 / +60 16-498 8989</t>
         </is>
       </c>
       <c r="J491" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7306962</t>
+          <t>+60 4-730 6962</t>
         </is>
       </c>
       <c r="K491" s="8" t="inlineStr">
@@ -21629,12 +21625,12 @@
       </c>
       <c r="I492" s="6" t="inlineStr">
         <is>
-          <t>+6017-4739739</t>
+          <t>+60 17-473 9739</t>
         </is>
       </c>
       <c r="J492" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7334577</t>
+          <t>+60 4-733 4577</t>
         </is>
       </c>
       <c r="K492" s="6" t="inlineStr">
@@ -21687,12 +21683,12 @@
       </c>
       <c r="I493" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4770888</t>
+          <t>+60 19-477 0888</t>
         </is>
       </c>
       <c r="J493" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7333688, 7300612</t>
+          <t>+60 4-733 3688</t>
         </is>
       </c>
       <c r="K493" s="8" t="inlineStr">
@@ -21745,12 +21741,12 @@
       </c>
       <c r="I494" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4223404</t>
+          <t>+60 12-422 3404</t>
         </is>
       </c>
       <c r="J494" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7461285</t>
+          <t>+60 4-746 1285</t>
         </is>
       </c>
       <c r="K494" s="6" t="inlineStr">
@@ -21799,12 +21795,12 @@
       <c r="H495" s="8" t="inlineStr"/>
       <c r="I495" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 5327788</t>
+          <t>+60 12-532 7788</t>
         </is>
       </c>
       <c r="J495" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7315648 , / +604 - 7317788</t>
+          <t>+60 4-731 5648 / +60 4-731 7788</t>
         </is>
       </c>
       <c r="K495" s="8" t="inlineStr">
@@ -21853,12 +21849,12 @@
       <c r="H496" s="6" t="inlineStr"/>
       <c r="I496" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4446024</t>
+          <t>+60 19-444 6024</t>
         </is>
       </c>
       <c r="J496" s="6" t="inlineStr">
         <is>
-          <t>+604 - 7333332 , / +604 - 7328348</t>
+          <t>+60 4-733 3332 / +60 4-732 8348</t>
         </is>
       </c>
       <c r="K496" s="6" t="inlineStr">
@@ -21911,12 +21907,12 @@
       </c>
       <c r="I497" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4301794</t>
+          <t>+60 19-430 1794</t>
         </is>
       </c>
       <c r="J497" s="8" t="inlineStr">
         <is>
-          <t>+604 - 7295420</t>
+          <t>+60 4-729 5420</t>
         </is>
       </c>
       <c r="K497" s="8" t="inlineStr">
@@ -52965,7 +52961,7 @@
       </c>
       <c r="E45" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4230006</t>
+          <t>+60 12-423 0006</t>
         </is>
       </c>
       <c r="F45" s="8" t="inlineStr">
@@ -53005,7 +53001,7 @@
       </c>
       <c r="E46" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4504285</t>
+          <t>+60 19-450 4285</t>
         </is>
       </c>
       <c r="F46" s="6" t="inlineStr">
@@ -53045,7 +53041,7 @@
       </c>
       <c r="E47" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4407296</t>
+          <t>+60 19-440 7296</t>
         </is>
       </c>
       <c r="F47" s="8" t="inlineStr">
@@ -53085,7 +53081,7 @@
       </c>
       <c r="E48" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4252563</t>
+          <t>+60 12-425 2563</t>
         </is>
       </c>
       <c r="F48" s="6" t="inlineStr">
@@ -53125,7 +53121,7 @@
       </c>
       <c r="E49" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4011283</t>
+          <t>+60 12-401 1283</t>
         </is>
       </c>
       <c r="F49" s="8" t="inlineStr">
@@ -53165,7 +53161,7 @@
       </c>
       <c r="E50" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4107607</t>
+          <t>+60 12-410 7607</t>
         </is>
       </c>
       <c r="F50" s="6" t="inlineStr">
@@ -53205,7 +53201,7 @@
       </c>
       <c r="E51" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4406515</t>
+          <t>+60 19-440 6515</t>
         </is>
       </c>
       <c r="F51" s="8" t="inlineStr">
@@ -53245,7 +53241,7 @@
       </c>
       <c r="E52" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4413922</t>
+          <t>+60 19-441 3922</t>
         </is>
       </c>
       <c r="F52" s="6" t="inlineStr">
@@ -53285,7 +53281,7 @@
       </c>
       <c r="E53" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4501026</t>
+          <t>+60 19-450 1026</t>
         </is>
       </c>
       <c r="F53" s="8" t="inlineStr">
@@ -53325,7 +53321,7 @@
       </c>
       <c r="E54" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4212079</t>
+          <t>+60 12-421 2079</t>
         </is>
       </c>
       <c r="F54" s="6" t="inlineStr">
@@ -53365,7 +53361,7 @@
       </c>
       <c r="E55" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4006633</t>
+          <t>+60 12-400 6633</t>
         </is>
       </c>
       <c r="F55" s="8" t="inlineStr">
@@ -53405,7 +53401,7 @@
       </c>
       <c r="E56" s="6" t="inlineStr">
         <is>
-          <t>+6017 - 4697789</t>
+          <t>+60 17-469 7789</t>
         </is>
       </c>
       <c r="F56" s="6" t="inlineStr">
@@ -53445,7 +53441,7 @@
       </c>
       <c r="E57" s="8" t="inlineStr">
         <is>
-          <t>+6017 - 4192388</t>
+          <t>+60 17-419 2388</t>
         </is>
       </c>
       <c r="F57" s="8" t="inlineStr">
@@ -53485,7 +53481,7 @@
       </c>
       <c r="E58" s="6" t="inlineStr">
         <is>
-          <t>+012 - 4737141</t>
+          <t>+60 12-473 7141</t>
         </is>
       </c>
       <c r="F58" s="6" t="inlineStr">
@@ -53525,7 +53521,7 @@
       </c>
       <c r="E59" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4330039</t>
+          <t>+60 12-433 0039</t>
         </is>
       </c>
       <c r="F59" s="8" t="inlineStr">
@@ -53565,7 +53561,7 @@
       </c>
       <c r="E60" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 5996185</t>
+          <t>+60 12-599 6185</t>
         </is>
       </c>
       <c r="F60" s="6" t="inlineStr">
@@ -53601,7 +53597,7 @@
       </c>
       <c r="E61" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4323388</t>
+          <t>+60 12-432 3388</t>
         </is>
       </c>
       <c r="F61" s="8" t="inlineStr">
@@ -53641,7 +53637,7 @@
       </c>
       <c r="E62" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4719888</t>
+          <t>+60 12-471 9888</t>
         </is>
       </c>
       <c r="F62" s="6" t="inlineStr">
@@ -53681,7 +53677,7 @@
       </c>
       <c r="E63" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4824350</t>
+          <t>+60 12-482 4350</t>
         </is>
       </c>
       <c r="F63" s="8" t="inlineStr">
@@ -53721,7 +53717,7 @@
       </c>
       <c r="E64" s="6" t="inlineStr">
         <is>
-          <t>+6013 - 4281936</t>
+          <t>+60 13-428 1936</t>
         </is>
       </c>
       <c r="F64" s="6" t="inlineStr">
@@ -53761,7 +53757,7 @@
       </c>
       <c r="E65" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 2388732</t>
+          <t>+60 19-238 8732</t>
         </is>
       </c>
       <c r="F65" s="8" t="inlineStr">
@@ -53801,7 +53797,7 @@
       </c>
       <c r="E66" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4933666</t>
+          <t>+60 12-493 3666</t>
         </is>
       </c>
       <c r="F66" s="6" t="inlineStr">
@@ -53841,7 +53837,7 @@
       </c>
       <c r="E67" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 428 9362</t>
+          <t>+60 12-428 9362</t>
         </is>
       </c>
       <c r="F67" s="8" t="inlineStr">
@@ -53881,7 +53877,7 @@
       </c>
       <c r="E68" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4772333</t>
+          <t>+60 12-477 2333</t>
         </is>
       </c>
       <c r="F68" s="6" t="inlineStr">
@@ -53921,7 +53917,7 @@
       </c>
       <c r="E69" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4407369</t>
+          <t>+60 19-440 7369</t>
         </is>
       </c>
       <c r="F69" s="8" t="inlineStr">
@@ -53961,7 +53957,7 @@
       </c>
       <c r="E70" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 7500899</t>
+          <t>+60 12-750 0899</t>
         </is>
       </c>
       <c r="F70" s="6" t="inlineStr">
@@ -54001,7 +53997,7 @@
       </c>
       <c r="E71" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 2592328</t>
+          <t>+60 19-259 2328</t>
         </is>
       </c>
       <c r="F71" s="8" t="inlineStr">
@@ -54041,7 +54037,7 @@
       </c>
       <c r="E72" s="6" t="inlineStr">
         <is>
-          <t>+6016 - 4404826</t>
+          <t>+60 16-440 4826</t>
         </is>
       </c>
       <c r="F72" s="6" t="inlineStr">
@@ -54081,7 +54077,7 @@
       </c>
       <c r="E73" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4408819</t>
+          <t>+60 19-440 8819</t>
         </is>
       </c>
       <c r="F73" s="8" t="inlineStr">
@@ -54121,7 +54117,7 @@
       </c>
       <c r="E74" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4406525</t>
+          <t>+60 19-440 6525</t>
         </is>
       </c>
       <c r="F74" s="6" t="inlineStr">
@@ -54161,7 +54157,7 @@
       </c>
       <c r="E75" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4443834</t>
+          <t>+60 19-444 3834</t>
         </is>
       </c>
       <c r="F75" s="8" t="inlineStr">
@@ -54201,7 +54197,7 @@
       </c>
       <c r="E76" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 4942523</t>
+          <t>+60 12-494 2523</t>
         </is>
       </c>
       <c r="F76" s="6" t="inlineStr">
@@ -54241,7 +54237,7 @@
       </c>
       <c r="E77" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4842255</t>
+          <t>+60 12-484 2255</t>
         </is>
       </c>
       <c r="F77" s="8" t="inlineStr">
@@ -54281,7 +54277,7 @@
       </c>
       <c r="E78" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 5261002</t>
+          <t>+60 12-526 1002</t>
         </is>
       </c>
       <c r="F78" s="6" t="inlineStr">
@@ -54321,7 +54317,7 @@
       </c>
       <c r="E79" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4892348</t>
+          <t>+60 12-489 2348</t>
         </is>
       </c>
       <c r="F79" s="8" t="inlineStr">
@@ -54361,7 +54357,7 @@
       </c>
       <c r="E80" s="6" t="inlineStr">
         <is>
-          <t>+6016 - 4218989, 016 - 4988989</t>
+          <t>+60 16-421 8989 / +60 16-498 8989</t>
         </is>
       </c>
       <c r="F80" s="6" t="inlineStr">
@@ -54401,7 +54397,7 @@
       </c>
       <c r="E81" s="8" t="inlineStr">
         <is>
-          <t>+6017-4739739</t>
+          <t>+60 17-473 9739</t>
         </is>
       </c>
       <c r="F81" s="8" t="inlineStr">
@@ -54441,7 +54437,7 @@
       </c>
       <c r="E82" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4770888</t>
+          <t>+60 19-477 0888</t>
         </is>
       </c>
       <c r="F82" s="6" t="inlineStr">
@@ -54481,7 +54477,7 @@
       </c>
       <c r="E83" s="8" t="inlineStr">
         <is>
-          <t>+6012 - 4223404</t>
+          <t>+60 12-422 3404</t>
         </is>
       </c>
       <c r="F83" s="8" t="inlineStr">
@@ -54521,7 +54517,7 @@
       </c>
       <c r="E84" s="6" t="inlineStr">
         <is>
-          <t>+6012 - 5327788</t>
+          <t>+60 12-532 7788</t>
         </is>
       </c>
       <c r="F84" s="6" t="inlineStr">
@@ -54561,7 +54557,7 @@
       </c>
       <c r="E85" s="8" t="inlineStr">
         <is>
-          <t>+6019 - 4446024</t>
+          <t>+60 19-444 6024</t>
         </is>
       </c>
       <c r="F85" s="8" t="inlineStr">
@@ -54601,7 +54597,7 @@
       </c>
       <c r="E86" s="6" t="inlineStr">
         <is>
-          <t>+6019 - 4301794</t>
+          <t>+60 19-430 1794</t>
         </is>
       </c>
       <c r="F86" s="6" t="inlineStr">
